--- a/NG_flows_scm_output.xlsx
+++ b/NG_flows_scm_output.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/scm_model/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3A83012E7BF9101CC4FF31D2F8F2D3C2D4D26FB3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -61,8 +55,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,25 +115,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +163,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -211,7 +197,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -246,10 +231,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -422,11 +406,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E217"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -443,7 +427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>2026</v>
       </c>
@@ -457,10 +441,10 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>43.900036572472978</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>91.34670793567381</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2026</v>
       </c>
@@ -477,7 +461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -494,7 +478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>2026</v>
       </c>
@@ -511,7 +495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>2026</v>
       </c>
@@ -525,10 +509,10 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>11.812967958185389</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11.81296795818539</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>2026</v>
       </c>
@@ -545,7 +529,7 @@
         <v>141.4333423124618</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>2026</v>
       </c>
@@ -562,7 +546,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>2026</v>
       </c>
@@ -576,10 +560,10 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>404.81599481948882</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>404.8159948194888</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>2026</v>
       </c>
@@ -593,10 +577,10 @@
         <v>8</v>
       </c>
       <c r="E10">
-        <v>48.467335167527011</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100.8502920643262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>2030</v>
       </c>
@@ -610,10 +594,10 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <v>28.073099119979691</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28.07309911997969</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>2030</v>
       </c>
@@ -630,7 +614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>2030</v>
       </c>
@@ -647,7 +631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>2030</v>
       </c>
@@ -664,7 +648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>2030</v>
       </c>
@@ -678,10 +662,10 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>9.8816510339669801</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9.88165103396698</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2030</v>
       </c>
@@ -695,10 +679,10 @@
         <v>8</v>
       </c>
       <c r="E16">
-        <v>118.31022806854629</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>118.3102280685463</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2030</v>
       </c>
@@ -715,7 +699,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>2030</v>
       </c>
@@ -729,10 +713,10 @@
         <v>8</v>
       </c>
       <c r="E18">
-        <v>338.63212089748669</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>338.6321208974867</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>2030</v>
       </c>
@@ -746,10 +730,10 @@
         <v>8</v>
       </c>
       <c r="E19">
-        <v>30.993785210020299</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30.9937852100203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>2035</v>
       </c>
@@ -763,10 +747,10 @@
         <v>8</v>
       </c>
       <c r="E20">
-        <v>27.939162342756621</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27.93916234275662</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>2035</v>
       </c>
@@ -783,7 +767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>2035</v>
       </c>
@@ -800,7 +784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>2035</v>
       </c>
@@ -817,7 +801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>2035</v>
       </c>
@@ -834,7 +818,7 @@
         <v>6.951367170491487</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>2035</v>
       </c>
@@ -848,10 +832,10 @@
         <v>8</v>
       </c>
       <c r="E25">
-        <v>83.226763675633933</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>83.22676367563393</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>2035</v>
       </c>
@@ -868,7 +852,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -885,7 +869,7 @@
         <v>238.2148691538745</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>2035</v>
       </c>
@@ -899,10 +883,10 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>30.845913837243369</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30.84591383724337</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>2040</v>
       </c>
@@ -916,10 +900,10 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <v>47.013994948645028</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>47.01399494864503</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>2040</v>
       </c>
@@ -936,7 +920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>2040</v>
       </c>
@@ -953,7 +937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -970,7 +954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>2040</v>
       </c>
@@ -984,10 +968,10 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>5.3565405287568293</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.356540528756829</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>2040</v>
       </c>
@@ -1001,10 +985,10 @@
         <v>8</v>
       </c>
       <c r="E34">
-        <v>64.132352927385313</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>64.13235292738531</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>2040</v>
       </c>
@@ -1021,7 +1005,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>2040</v>
       </c>
@@ -1035,10 +1019,10 @@
         <v>8</v>
       </c>
       <c r="E36">
-        <v>183.56210654385791</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>183.5621065438579</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>2040</v>
       </c>
@@ -1055,7 +1039,7 @@
         <v>51.90526543135497</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>2045</v>
       </c>
@@ -1069,10 +1053,10 @@
         <v>8</v>
       </c>
       <c r="E38">
-        <v>50.179985896702192</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>50.17998589670219</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>2045</v>
       </c>
@@ -1089,7 +1073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>2045</v>
       </c>
@@ -1106,7 +1090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>2045</v>
       </c>
@@ -1123,7 +1107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>2045</v>
       </c>
@@ -1137,10 +1121,10 @@
         <v>8</v>
       </c>
       <c r="E42">
-        <v>4.1055641162215259</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4.105564116221526</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>2045</v>
       </c>
@@ -1154,10 +1138,10 @@
         <v>8</v>
       </c>
       <c r="E43">
-        <v>49.154764246437132</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>49.15476424643713</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>2045</v>
       </c>
@@ -1174,7 +1158,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>2045</v>
       </c>
@@ -1188,10 +1172,10 @@
         <v>8</v>
       </c>
       <c r="E45">
-        <v>140.69267163734131</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>140.6926716373413</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>2045</v>
       </c>
@@ -1205,10 +1189,10 @@
         <v>8</v>
       </c>
       <c r="E46">
-        <v>55.400641663297797</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>55.4006416632978</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>2050</v>
       </c>
@@ -1222,10 +1206,10 @@
         <v>8</v>
       </c>
       <c r="E47">
-        <v>47.501061705512093</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>47.50106170551209</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>2050</v>
       </c>
@@ -1242,7 +1226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>2050</v>
       </c>
@@ -1259,7 +1243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50">
         <v>2050</v>
       </c>
@@ -1276,7 +1260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>2050</v>
       </c>
@@ -1293,7 +1277,7 @@
         <v>3.905083599061522</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>2050</v>
       </c>
@@ -1307,10 +1291,10 @@
         <v>8</v>
       </c>
       <c r="E52">
-        <v>46.754467410719172</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46.75446741071917</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>2050</v>
       </c>
@@ -1327,7 +1311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>2050</v>
       </c>
@@ -1344,7 +1328,7 @@
         <v>133.8224489902193</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>2050</v>
       </c>
@@ -1358,10 +1342,10 @@
         <v>8</v>
       </c>
       <c r="E55">
-        <v>52.443005934487907</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>52.44300593448791</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56">
         <v>2026</v>
       </c>
@@ -1375,10 +1359,10 @@
         <v>9</v>
       </c>
       <c r="E56">
-        <v>51.33081286985923</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>32.49274980738656</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57">
         <v>2026</v>
       </c>
@@ -1395,7 +1379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58">
         <v>2026</v>
       </c>
@@ -1412,7 +1396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59">
         <v>2026</v>
       </c>
@@ -1429,7 +1413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>2026</v>
       </c>
@@ -1443,10 +1427,10 @@
         <v>9</v>
       </c>
       <c r="E60">
-        <v>18.717144561125838</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>18.71714456112584</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61">
         <v>2026</v>
       </c>
@@ -1460,10 +1444,10 @@
         <v>9</v>
       </c>
       <c r="E61">
-        <v>224.09510659776549</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224.0951065977655</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>2026</v>
       </c>
@@ -1477,10 +1461,10 @@
         <v>9</v>
       </c>
       <c r="E62">
-        <v>7.7777777777777777</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7.777777777777778</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63">
         <v>2026</v>
       </c>
@@ -1494,10 +1478,10 @@
         <v>9</v>
       </c>
       <c r="E63">
-        <v>641.41370081700052</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>641.4137008170005</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64">
         <v>2026</v>
       </c>
@@ -1511,10 +1495,10 @@
         <v>9</v>
       </c>
       <c r="E64">
-        <v>56.671199070140773</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>35.87325019261343</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65">
         <v>2030</v>
       </c>
@@ -1528,10 +1512,10 @@
         <v>9</v>
       </c>
       <c r="E65">
-        <v>39.832212400033853</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>39.83221240003385</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66">
         <v>2030</v>
       </c>
@@ -1548,7 +1532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67">
         <v>2030</v>
       </c>
@@ -1565,7 +1549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68">
         <v>2030</v>
       </c>
@@ -1582,7 +1566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69">
         <v>2030</v>
       </c>
@@ -1596,10 +1580,10 @@
         <v>9</v>
       </c>
       <c r="E69">
-        <v>14.610653842703581</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14.61065384270358</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70">
         <v>2030</v>
       </c>
@@ -1613,10 +1597,10 @@
         <v>9</v>
       </c>
       <c r="E70">
-        <v>174.92924840383711</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>174.9292484038371</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71">
         <v>2030</v>
       </c>
@@ -1630,10 +1614,10 @@
         <v>9</v>
       </c>
       <c r="E71">
-        <v>5.9722222222222223</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.972222222222222</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72">
         <v>2030</v>
       </c>
@@ -1647,10 +1631,10 @@
         <v>9</v>
       </c>
       <c r="E72">
-        <v>500.68927565310952</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>500.6892756531095</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73">
         <v>2030</v>
       </c>
@@ -1667,7 +1651,7 @@
         <v>43.97630023996615</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74">
         <v>2035</v>
       </c>
@@ -1681,10 +1665,10 @@
         <v>9</v>
       </c>
       <c r="E74">
-        <v>23.706679694440709</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>23.70667969444071</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75">
         <v>2035</v>
       </c>
@@ -1701,7 +1685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76">
         <v>2035</v>
       </c>
@@ -1718,7 +1702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77">
         <v>2035</v>
       </c>
@@ -1735,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78">
         <v>2035</v>
       </c>
@@ -1752,7 +1736,7 @@
         <v>10.90299599509941</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79">
         <v>2035</v>
       </c>
@@ -1766,10 +1750,10 @@
         <v>9</v>
       </c>
       <c r="E79">
-        <v>130.53850397839989</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>130.5385039783999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80">
         <v>2035</v>
       </c>
@@ -1786,7 +1770,7 @@
         <v>4.166666666666667</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81">
         <v>2035</v>
       </c>
@@ -1800,10 +1784,10 @@
         <v>9</v>
       </c>
       <c r="E81">
-        <v>373.63236621756351</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>373.6323662175635</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82">
         <v>2035</v>
       </c>
@@ -1820,7 +1804,7 @@
         <v>26.17308959555929</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83">
         <v>2040</v>
       </c>
@@ -1834,10 +1818,10 @@
         <v>9</v>
       </c>
       <c r="E83">
-        <v>12.393484781787009</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>12.39348478178701</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84">
         <v>2040</v>
       </c>
@@ -1854,7 +1838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85">
         <v>2040</v>
       </c>
@@ -1871,7 +1855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86">
         <v>2040</v>
       </c>
@@ -1888,7 +1872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87">
         <v>2040</v>
       </c>
@@ -1902,10 +1886,10 @@
         <v>9</v>
       </c>
       <c r="E87">
-        <v>7.5610706908851792</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7.561070690885179</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88">
         <v>2040</v>
       </c>
@@ -1919,10 +1903,10 @@
         <v>9</v>
       </c>
       <c r="E88">
-        <v>90.526572412455437</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90.52657241245544</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89">
         <v>2040</v>
       </c>
@@ -1939,7 +1923,7 @@
         <v>4.166666666666667</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90">
         <v>2040</v>
       </c>
@@ -1953,10 +1937,10 @@
         <v>9</v>
       </c>
       <c r="E90">
-        <v>259.10866468661311</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>259.1086646866131</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91">
         <v>2040</v>
       </c>
@@ -1970,10 +1954,10 @@
         <v>9</v>
       </c>
       <c r="E91">
-        <v>13.682885658212991</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13.68288565821299</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92">
         <v>2045</v>
       </c>
@@ -1987,10 +1971,10 @@
         <v>9</v>
       </c>
       <c r="E92">
-        <v>8.5006597557527961</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8.500659755752796</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93">
         <v>2045</v>
       </c>
@@ -2007,7 +1991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94">
         <v>2045</v>
       </c>
@@ -2024,7 +2008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95">
         <v>2045</v>
       </c>
@@ -2041,7 +2025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96">
         <v>2045</v>
       </c>
@@ -2055,10 +2039,10 @@
         <v>9</v>
       </c>
       <c r="E96">
-        <v>5.6319616755606097</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.63196167556061</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97">
         <v>2045</v>
       </c>
@@ -2072,10 +2056,10 @@
         <v>9</v>
       </c>
       <c r="E97">
-        <v>67.429892840629407</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>67.42989284062941</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98">
         <v>2045</v>
       </c>
@@ -2092,7 +2076,7 @@
         <v>4.166666666666667</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99">
         <v>2045</v>
       </c>
@@ -2106,10 +2090,10 @@
         <v>9</v>
       </c>
       <c r="E99">
-        <v>193.00045310776611</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>193.0004531077661</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100">
         <v>2045</v>
       </c>
@@ -2123,10 +2107,10 @@
         <v>9</v>
       </c>
       <c r="E100">
-        <v>9.3850565442472025</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9.385056544247202</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101">
         <v>2050</v>
       </c>
@@ -2140,10 +2124,10 @@
         <v>9</v>
       </c>
       <c r="E101">
-        <v>5.2945372674418714</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.294537267441871</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102">
         <v>2050</v>
       </c>
@@ -2160,7 +2144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
       <c r="A103">
         <v>2050</v>
       </c>
@@ -2177,7 +2161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5">
       <c r="A104">
         <v>2050</v>
       </c>
@@ -2194,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5">
       <c r="A105">
         <v>2050</v>
       </c>
@@ -2208,10 +2192,10 @@
         <v>9</v>
       </c>
       <c r="E105">
-        <v>5.4810375941911236</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.481037594191124</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
       <c r="A106">
         <v>2050</v>
       </c>
@@ -2225,10 +2209,10 @@
         <v>9</v>
       </c>
       <c r="E106">
-        <v>65.622921270141603</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+        <v>65.6229212701416</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107">
         <v>2050</v>
       </c>
@@ -2245,7 +2229,7 @@
         <v>4.166666666666667</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5">
       <c r="A108">
         <v>2050</v>
       </c>
@@ -2262,7 +2246,7 @@
         <v>187.8284690341556</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5">
       <c r="A109">
         <v>2050</v>
       </c>
@@ -2276,10 +2260,10 @@
         <v>9</v>
       </c>
       <c r="E109">
-        <v>5.8453735425581277</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.845373542558128</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
       <c r="A110">
         <v>2026</v>
       </c>
@@ -2296,7 +2280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5">
       <c r="A111">
         <v>2026</v>
       </c>
@@ -2313,7 +2297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5">
       <c r="A112">
         <v>2026</v>
       </c>
@@ -2330,7 +2314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5">
       <c r="A113">
         <v>2026</v>
       </c>
@@ -2347,7 +2331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5">
       <c r="A114">
         <v>2026</v>
       </c>
@@ -2361,10 +2345,10 @@
         <v>10</v>
       </c>
       <c r="E114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.7863237762565295</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115">
         <v>2026</v>
       </c>
@@ -2378,10 +2362,10 @@
         <v>10</v>
       </c>
       <c r="E115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9.414433376047256</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116">
         <v>2026</v>
       </c>
@@ -2395,10 +2379,10 @@
         <v>10</v>
       </c>
       <c r="E116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.111111111111111</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
       <c r="A117">
         <v>2026</v>
       </c>
@@ -2412,10 +2396,10 @@
         <v>10</v>
       </c>
       <c r="E117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+        <v>26.94635614540354</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
       <c r="A118">
         <v>2026</v>
       </c>
@@ -2432,7 +2416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5">
       <c r="A119">
         <v>2030</v>
       </c>
@@ -2449,7 +2433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5">
       <c r="A120">
         <v>2030</v>
       </c>
@@ -2466,7 +2450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5">
       <c r="A121">
         <v>2030</v>
       </c>
@@ -2483,7 +2467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5">
       <c r="A122">
         <v>2030</v>
       </c>
@@ -2500,7 +2484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5">
       <c r="A123">
         <v>2030</v>
       </c>
@@ -2514,10 +2498,10 @@
         <v>10</v>
       </c>
       <c r="E123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.484470507347828</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
       <c r="A124">
         <v>2030</v>
       </c>
@@ -2531,10 +2515,10 @@
         <v>10</v>
       </c>
       <c r="E124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+        <v>17.77314779500431</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
       <c r="A125">
         <v>2030</v>
       </c>
@@ -2548,10 +2532,10 @@
         <v>10</v>
       </c>
       <c r="E125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.222222222222222</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
       <c r="A126">
         <v>2030</v>
       </c>
@@ -2565,10 +2549,10 @@
         <v>10</v>
       </c>
       <c r="E126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+        <v>50.87099256845129</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
       <c r="A127">
         <v>2030</v>
       </c>
@@ -2585,7 +2569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5">
       <c r="A128">
         <v>2035</v>
       </c>
@@ -2602,7 +2586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5">
       <c r="A129">
         <v>2035</v>
       </c>
@@ -2619,7 +2603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5">
       <c r="A130">
         <v>2035</v>
       </c>
@@ -2636,7 +2620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5">
       <c r="A131">
         <v>2035</v>
       </c>
@@ -2653,7 +2637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5">
       <c r="A132">
         <v>2035</v>
       </c>
@@ -2667,10 +2651,10 @@
         <v>10</v>
       </c>
       <c r="E132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.470180788882288</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
       <c r="A133">
         <v>2035</v>
       </c>
@@ -2684,10 +2668,10 @@
         <v>10</v>
       </c>
       <c r="E133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+        <v>17.60206101559042</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
       <c r="A134">
         <v>2035</v>
       </c>
@@ -2701,10 +2685,10 @@
         <v>10</v>
       </c>
       <c r="E134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.333333333333333</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135">
         <v>2035</v>
       </c>
@@ -2718,10 +2702,10 @@
         <v>10</v>
       </c>
       <c r="E135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+        <v>50.38130135648878</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
       <c r="A136">
         <v>2035</v>
       </c>
@@ -2738,7 +2722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5">
       <c r="A137">
         <v>2040</v>
       </c>
@@ -2755,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5">
       <c r="A138">
         <v>2040</v>
       </c>
@@ -2772,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5">
       <c r="A139">
         <v>2040</v>
       </c>
@@ -2789,7 +2773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5">
       <c r="A140">
         <v>2040</v>
       </c>
@@ -2806,7 +2790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5">
       <c r="A141">
         <v>2040</v>
       </c>
@@ -2820,10 +2804,10 @@
         <v>10</v>
       </c>
       <c r="E141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.8928594587863921</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
       <c r="A142">
         <v>2040</v>
       </c>
@@ -2837,10 +2821,10 @@
         <v>10</v>
       </c>
       <c r="E142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10.68995513392159</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
       <c r="A143">
         <v>2040</v>
       </c>
@@ -2854,10 +2838,10 @@
         <v>10</v>
       </c>
       <c r="E143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.888888888888889</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
       <c r="A144">
         <v>2040</v>
       </c>
@@ -2871,10 +2855,10 @@
         <v>10</v>
       </c>
       <c r="E144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30.5972039644917</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
       <c r="A145">
         <v>2040</v>
       </c>
@@ -2891,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5">
       <c r="A146">
         <v>2045</v>
       </c>
@@ -2908,7 +2892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5">
       <c r="A147">
         <v>2045</v>
       </c>
@@ -2925,7 +2909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5">
       <c r="A148">
         <v>2045</v>
       </c>
@@ -2942,7 +2926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5">
       <c r="A149">
         <v>2045</v>
       </c>
@@ -2959,7 +2943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5">
       <c r="A150">
         <v>2045</v>
       </c>
@@ -2973,10 +2957,10 @@
         <v>10</v>
       </c>
       <c r="E150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.4365368998486919</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
       <c r="A151">
         <v>2045</v>
       </c>
@@ -2990,10 +2974,10 @@
         <v>10</v>
       </c>
       <c r="E151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.226533501730162</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
       <c r="A152">
         <v>2045</v>
       </c>
@@ -3007,10 +2991,10 @@
         <v>10</v>
       </c>
       <c r="E152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.611111111111111</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
       <c r="A153">
         <v>2045</v>
       </c>
@@ -3024,10 +3008,10 @@
         <v>10</v>
       </c>
       <c r="E153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14.95958678743504</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
       <c r="A154">
         <v>2045</v>
       </c>
@@ -3044,7 +3028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5">
       <c r="A155">
         <v>2050</v>
       </c>
@@ -3061,7 +3045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5">
       <c r="A156">
         <v>2050</v>
       </c>
@@ -3078,7 +3062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5">
       <c r="A157">
         <v>2050</v>
       </c>
@@ -3095,7 +3079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5">
       <c r="A158">
         <v>2050</v>
       </c>
@@ -3112,7 +3096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5">
       <c r="A159">
         <v>2050</v>
       </c>
@@ -3126,10 +3110,10 @@
         <v>10</v>
       </c>
       <c r="E159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.2686680781182683</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
       <c r="A160">
         <v>2050</v>
       </c>
@@ -3143,10 +3127,10 @@
         <v>10</v>
       </c>
       <c r="E160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.216687321546693</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
       <c r="A161">
         <v>2050</v>
       </c>
@@ -3160,10 +3144,10 @@
         <v>10</v>
       </c>
       <c r="E161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.333333333333333</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
       <c r="A162">
         <v>2050</v>
       </c>
@@ -3177,10 +3161,10 @@
         <v>10</v>
       </c>
       <c r="E162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9.206927141821678</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
       <c r="A163">
         <v>2050</v>
       </c>
@@ -3197,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5">
       <c r="A164">
         <v>2026</v>
       </c>
@@ -3211,10 +3195,10 @@
         <v>11</v>
       </c>
       <c r="E164">
-        <v>186.05626926236491</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164.751729869112</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
       <c r="A165">
         <v>2026</v>
       </c>
@@ -3231,7 +3215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5">
       <c r="A166">
         <v>2026</v>
       </c>
@@ -3248,7 +3232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5">
       <c r="A167">
         <v>2026</v>
       </c>
@@ -3265,7 +3249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5">
       <c r="A168">
         <v>2026</v>
       </c>
@@ -3279,10 +3263,10 @@
         <v>11</v>
       </c>
       <c r="E168">
-        <v>25.647718742141141</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+        <v>24.14108574697975</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
       <c r="A169">
         <v>2026</v>
       </c>
@@ -3296,10 +3280,10 @@
         <v>11</v>
       </c>
       <c r="E169">
-        <v>307.07292165957989</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+        <v>289.0344286324099</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
       <c r="A170">
         <v>2026</v>
       </c>
@@ -3313,10 +3297,10 @@
         <v>11</v>
       </c>
       <c r="E170">
-        <v>3.6999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.037</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
       <c r="A171">
         <v>2026</v>
       </c>
@@ -3330,10 +3314,10 @@
         <v>11</v>
       </c>
       <c r="E171">
-        <v>878.91601959827881</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+        <v>827.2855456206103</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
       <c r="A172">
         <v>2026</v>
       </c>
@@ -3347,10 +3331,10 @@
         <v>11</v>
       </c>
       <c r="E172">
-        <v>205.41330409763509</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+        <v>181.8922701308881</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
       <c r="A173">
         <v>2030</v>
       </c>
@@ -3364,10 +3348,10 @@
         <v>11</v>
       </c>
       <c r="E173">
-        <v>180.38285541545281</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+        <v>180.3828554154528</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
       <c r="A174">
         <v>2030</v>
       </c>
@@ -3384,7 +3368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5">
       <c r="A175">
         <v>2030</v>
       </c>
@@ -3401,7 +3385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5">
       <c r="A176">
         <v>2030</v>
       </c>
@@ -3418,7 +3402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5">
       <c r="A177">
         <v>2030</v>
       </c>
@@ -3432,10 +3416,10 @@
         <v>11</v>
       </c>
       <c r="E177">
-        <v>14.544178222408441</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13.82385009432965</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
       <c r="A178">
         <v>2030</v>
       </c>
@@ -3449,10 +3433,10 @@
         <v>11</v>
       </c>
       <c r="E178">
-        <v>174.13335450199</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+        <v>165.5090684566469</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
       <c r="A179">
         <v>2030</v>
       </c>
@@ -3469,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5">
       <c r="A180">
         <v>2030</v>
       </c>
@@ -3483,10 +3467,10 @@
         <v>11</v>
       </c>
       <c r="E180">
-        <v>498.41123727560148</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+        <v>473.7264714490234</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
       <c r="A181">
         <v>2030</v>
       </c>
@@ -3500,10 +3484,10 @@
         <v>11</v>
       </c>
       <c r="E181">
-        <v>199.14963618454729</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+        <v>199.1496361845473</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
       <c r="A182">
         <v>2035</v>
       </c>
@@ -3520,7 +3504,7 @@
         <v>140.6104754109173</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5">
       <c r="A183">
         <v>2035</v>
       </c>
@@ -3537,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5">
       <c r="A184">
         <v>2035</v>
       </c>
@@ -3554,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5">
       <c r="A185">
         <v>2035</v>
       </c>
@@ -3571,7 +3555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5">
       <c r="A186">
         <v>2035</v>
       </c>
@@ -3585,10 +3569,10 @@
         <v>11</v>
       </c>
       <c r="E186">
-        <v>6.0238239801640558</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.668829735225702</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
       <c r="A187">
         <v>2035</v>
       </c>
@@ -3602,10 +3586,10 @@
         <v>11</v>
       </c>
       <c r="E187">
-        <v>72.121549980690148</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+        <v>67.87130374781773</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
       <c r="A188">
         <v>2035</v>
       </c>
@@ -3622,7 +3606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5">
       <c r="A189">
         <v>2035</v>
       </c>
@@ -3636,10 +3620,10 @@
         <v>11</v>
       </c>
       <c r="E189">
-        <v>206.4290960391458</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+        <v>194.2638765169566</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
       <c r="A190">
         <v>2035</v>
       </c>
@@ -3656,7 +3640,7 @@
         <v>155.2393932190827</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5">
       <c r="A191">
         <v>2040</v>
       </c>
@@ -3670,10 +3654,10 @@
         <v>11</v>
       </c>
       <c r="E191">
-        <v>77.982331301204681</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+        <v>77.98233130120468</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
       <c r="A192">
         <v>2040</v>
       </c>
@@ -3690,7 +3674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5">
       <c r="A193">
         <v>2040</v>
       </c>
@@ -3707,7 +3691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5">
       <c r="A194">
         <v>2040</v>
       </c>
@@ -3724,7 +3708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5">
       <c r="A195">
         <v>2040</v>
       </c>
@@ -3738,10 +3722,10 @@
         <v>11</v>
       </c>
       <c r="E195">
-        <v>1.8493181470020179</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.638094109445078</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
       <c r="A196">
         <v>2040</v>
       </c>
@@ -3755,10 +3739,10 @@
         <v>11</v>
       </c>
       <c r="E196">
-        <v>22.141365950996949</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+        <v>19.61243996777606</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
       <c r="A197">
         <v>2040</v>
       </c>
@@ -3775,7 +3759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5">
       <c r="A198">
         <v>2040</v>
       </c>
@@ -3789,10 +3773,10 @@
         <v>11</v>
       </c>
       <c r="E198">
-        <v>63.373875902001018</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+        <v>56.13548592277887</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
       <c r="A199">
         <v>2040</v>
       </c>
@@ -3806,10 +3790,10 @@
         <v>11</v>
       </c>
       <c r="E199">
-        <v>86.095504318795321</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+        <v>86.09550431879532</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
       <c r="A200">
         <v>2045</v>
       </c>
@@ -3826,7 +3810,7 @@
         <v>29.42410936394722</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5">
       <c r="A201">
         <v>2045</v>
       </c>
@@ -3843,7 +3827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5">
       <c r="A202">
         <v>2045</v>
       </c>
@@ -3860,7 +3844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5">
       <c r="A203">
         <v>2045</v>
       </c>
@@ -3877,7 +3861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5">
       <c r="A204">
         <v>2045</v>
       </c>
@@ -3891,10 +3875,10 @@
         <v>11</v>
       </c>
       <c r="E204">
-        <v>2.1176563765323961</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.920218523244907</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
       <c r="A205">
         <v>2045</v>
       </c>
@@ -3908,10 +3892,10 @@
         <v>11</v>
       </c>
       <c r="E205">
-        <v>25.354104088189001</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+        <v>22.99023621109907</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
       <c r="A206">
         <v>2045</v>
       </c>
@@ -3928,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5">
       <c r="A207">
         <v>2045</v>
       </c>
@@ -3942,10 +3926,10 @@
         <v>11</v>
       </c>
       <c r="E207">
-        <v>72.569499535278595</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+        <v>65.80354526565601</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
       <c r="A208">
         <v>2045</v>
       </c>
@@ -3959,10 +3943,10 @@
         <v>11</v>
       </c>
       <c r="E208">
-        <v>32.485352676052777</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+        <v>32.48535267605278</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
       <c r="A209">
         <v>2050</v>
       </c>
@@ -3979,7 +3963,7 @@
         <v>1.328835503507124</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5">
       <c r="A210">
         <v>2050</v>
       </c>
@@ -3996,7 +3980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5">
       <c r="A211">
         <v>2050</v>
       </c>
@@ -4013,7 +3997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5">
       <c r="A212">
         <v>2050</v>
       </c>
@@ -4030,7 +4014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5">
       <c r="A213">
         <v>2050</v>
       </c>
@@ -4044,10 +4028,10 @@
         <v>11</v>
       </c>
       <c r="E213">
-        <v>2.1097785569498528</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.945821436888173</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
       <c r="A214">
         <v>2050</v>
       </c>
@@ -4061,10 +4045,10 @@
         <v>11</v>
       </c>
       <c r="E214">
-        <v>25.25978517039988</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+        <v>23.29677269391372</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
       <c r="A215">
         <v>2050</v>
       </c>
@@ -4081,7 +4065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5">
       <c r="A216">
         <v>2050</v>
       </c>
@@ -4095,10 +4079,10 @@
         <v>11</v>
       </c>
       <c r="E216">
-        <v>72.299536272650272</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+        <v>66.68092586919809</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
       <c r="A217">
         <v>2050</v>
       </c>
@@ -4112,7 +4096,7 @@
         <v>11</v>
       </c>
       <c r="E217">
-        <v>1.4670856964928769</v>
+        <v>1.467085696492877</v>
       </c>
     </row>
   </sheetData>

--- a/NG_flows_scm_output.xlsx
+++ b/NG_flows_scm_output.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/scm_model/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_198B012E0101160AD2FE31D2F8F2D3C294D75243" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-28920" yWindow="6825" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -55,8 +61,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,17 +121,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -163,7 +177,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -197,6 +211,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -231,9 +246,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -406,11 +422,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E217"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -427,7 +443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2026</v>
       </c>
@@ -441,10 +457,10 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>91.34670793567381</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>91.346707935673805</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2026</v>
       </c>
@@ -461,7 +477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -478,7 +494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2026</v>
       </c>
@@ -495,7 +511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2026</v>
       </c>
@@ -509,10 +525,10 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>11.81296795818539</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>11.812967958185389</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2026</v>
       </c>
@@ -529,7 +545,7 @@
         <v>141.4333423124618</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2026</v>
       </c>
@@ -546,7 +562,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2026</v>
       </c>
@@ -560,10 +576,10 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>404.8159948194888</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>404.81599481948882</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2026</v>
       </c>
@@ -580,7 +596,7 @@
         <v>100.8502920643262</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2030</v>
       </c>
@@ -594,10 +610,10 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <v>28.07309911997969</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>28.073099119979691</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2030</v>
       </c>
@@ -614,7 +630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2030</v>
       </c>
@@ -631,7 +647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2030</v>
       </c>
@@ -648,7 +664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2030</v>
       </c>
@@ -662,10 +678,10 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>9.88165103396698</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>9.8816510339669801</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2030</v>
       </c>
@@ -679,10 +695,10 @@
         <v>8</v>
       </c>
       <c r="E16">
-        <v>118.3102280685463</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>118.31022806854629</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2030</v>
       </c>
@@ -699,7 +715,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2030</v>
       </c>
@@ -713,10 +729,10 @@
         <v>8</v>
       </c>
       <c r="E18">
-        <v>338.6321208974867</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>338.63212089748669</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2030</v>
       </c>
@@ -730,10 +746,10 @@
         <v>8</v>
       </c>
       <c r="E19">
-        <v>30.9937852100203</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>30.993785210020299</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2035</v>
       </c>
@@ -747,10 +763,10 @@
         <v>8</v>
       </c>
       <c r="E20">
-        <v>27.93916234275662</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>27.939162342756621</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2035</v>
       </c>
@@ -767,7 +783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2035</v>
       </c>
@@ -784,7 +800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2035</v>
       </c>
@@ -801,7 +817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2035</v>
       </c>
@@ -818,7 +834,7 @@
         <v>6.951367170491487</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2035</v>
       </c>
@@ -832,10 +848,10 @@
         <v>8</v>
       </c>
       <c r="E25">
-        <v>83.22676367563393</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>83.226763675633933</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2035</v>
       </c>
@@ -852,7 +868,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
@@ -869,7 +885,7 @@
         <v>238.2148691538745</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2035</v>
       </c>
@@ -883,10 +899,10 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>30.84591383724337</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>30.845913837243369</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2040</v>
       </c>
@@ -900,10 +916,10 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <v>47.01399494864503</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>47.013994948645028</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2040</v>
       </c>
@@ -920,7 +936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2040</v>
       </c>
@@ -937,7 +953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2040</v>
       </c>
@@ -954,7 +970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2040</v>
       </c>
@@ -968,10 +984,10 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>5.356540528756829</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>5.3565405287568293</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2040</v>
       </c>
@@ -985,10 +1001,10 @@
         <v>8</v>
       </c>
       <c r="E34">
-        <v>64.13235292738531</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>64.132352927385313</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2040</v>
       </c>
@@ -1005,7 +1021,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2040</v>
       </c>
@@ -1019,10 +1035,10 @@
         <v>8</v>
       </c>
       <c r="E36">
-        <v>183.5621065438579</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>183.56210654385791</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2040</v>
       </c>
@@ -1039,7 +1055,7 @@
         <v>51.90526543135497</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2045</v>
       </c>
@@ -1053,10 +1069,10 @@
         <v>8</v>
       </c>
       <c r="E38">
-        <v>50.17998589670219</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>50.179985896702192</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2045</v>
       </c>
@@ -1073,7 +1089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2045</v>
       </c>
@@ -1090,7 +1106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2045</v>
       </c>
@@ -1107,7 +1123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2045</v>
       </c>
@@ -1121,10 +1137,10 @@
         <v>8</v>
       </c>
       <c r="E42">
-        <v>4.105564116221526</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>4.1055641162215259</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2045</v>
       </c>
@@ -1138,10 +1154,10 @@
         <v>8</v>
       </c>
       <c r="E43">
-        <v>49.15476424643713</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>49.154764246437132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2045</v>
       </c>
@@ -1158,7 +1174,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2045</v>
       </c>
@@ -1172,10 +1188,10 @@
         <v>8</v>
       </c>
       <c r="E45">
-        <v>140.6926716373413</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>140.69267163734131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2045</v>
       </c>
@@ -1189,10 +1205,10 @@
         <v>8</v>
       </c>
       <c r="E46">
-        <v>55.4006416632978</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>55.400641663297797</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2050</v>
       </c>
@@ -1206,10 +1222,10 @@
         <v>8</v>
       </c>
       <c r="E47">
-        <v>47.50106170551209</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>47.501061705512093</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2050</v>
       </c>
@@ -1226,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2050</v>
       </c>
@@ -1243,7 +1259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2050</v>
       </c>
@@ -1260,7 +1276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2050</v>
       </c>
@@ -1277,7 +1293,7 @@
         <v>3.905083599061522</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2050</v>
       </c>
@@ -1291,10 +1307,10 @@
         <v>8</v>
       </c>
       <c r="E52">
-        <v>46.75446741071917</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>46.754467410719172</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2050</v>
       </c>
@@ -1311,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2050</v>
       </c>
@@ -1328,7 +1344,7 @@
         <v>133.8224489902193</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2050</v>
       </c>
@@ -1342,10 +1358,10 @@
         <v>8</v>
       </c>
       <c r="E55">
-        <v>52.44300593448791</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>52.443005934487907</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2026</v>
       </c>
@@ -1359,10 +1375,10 @@
         <v>9</v>
       </c>
       <c r="E56">
-        <v>32.49274980738656</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>32.492749807386559</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2026</v>
       </c>
@@ -1379,7 +1395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2026</v>
       </c>
@@ -1396,7 +1412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2026</v>
       </c>
@@ -1413,7 +1429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2026</v>
       </c>
@@ -1427,10 +1443,10 @@
         <v>9</v>
       </c>
       <c r="E60">
-        <v>18.71714456112584</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>18.717144561125838</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2026</v>
       </c>
@@ -1444,10 +1460,10 @@
         <v>9</v>
       </c>
       <c r="E61">
-        <v>224.0951065977655</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>224.09510659776549</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2026</v>
       </c>
@@ -1461,10 +1477,10 @@
         <v>9</v>
       </c>
       <c r="E62">
-        <v>7.777777777777778</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>7.7777777777777777</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2026</v>
       </c>
@@ -1478,10 +1494,10 @@
         <v>9</v>
       </c>
       <c r="E63">
-        <v>641.4137008170005</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>641.41370081700052</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2026</v>
       </c>
@@ -1495,10 +1511,10 @@
         <v>9</v>
       </c>
       <c r="E64">
-        <v>35.87325019261343</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>35.873250192613433</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2030</v>
       </c>
@@ -1512,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="E65">
-        <v>39.83221240003385</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>39.832212400033853</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2030</v>
       </c>
@@ -1532,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2030</v>
       </c>
@@ -1549,7 +1565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2030</v>
       </c>
@@ -1566,7 +1582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2030</v>
       </c>
@@ -1580,10 +1596,10 @@
         <v>9</v>
       </c>
       <c r="E69">
-        <v>14.61065384270358</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>14.610653842703581</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2030</v>
       </c>
@@ -1597,10 +1613,10 @@
         <v>9</v>
       </c>
       <c r="E70">
-        <v>174.9292484038371</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>174.92924840383711</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2030</v>
       </c>
@@ -1614,10 +1630,10 @@
         <v>9</v>
       </c>
       <c r="E71">
-        <v>5.972222222222222</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>5.9722222222222223</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2030</v>
       </c>
@@ -1631,10 +1647,10 @@
         <v>9</v>
       </c>
       <c r="E72">
-        <v>500.6892756531095</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>500.68927565310952</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2030</v>
       </c>
@@ -1651,7 +1667,7 @@
         <v>43.97630023996615</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2035</v>
       </c>
@@ -1665,10 +1681,10 @@
         <v>9</v>
       </c>
       <c r="E74">
-        <v>23.70667969444071</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>23.706679694440709</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2035</v>
       </c>
@@ -1685,7 +1701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2035</v>
       </c>
@@ -1702,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2035</v>
       </c>
@@ -1719,7 +1735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2035</v>
       </c>
@@ -1736,7 +1752,7 @@
         <v>10.90299599509941</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2035</v>
       </c>
@@ -1750,10 +1766,10 @@
         <v>9</v>
       </c>
       <c r="E79">
-        <v>130.5385039783999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>130.53850397839989</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2035</v>
       </c>
@@ -1770,7 +1786,7 @@
         <v>4.166666666666667</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2035</v>
       </c>
@@ -1784,10 +1800,10 @@
         <v>9</v>
       </c>
       <c r="E81">
-        <v>373.6323662175635</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>373.63236621756351</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2035</v>
       </c>
@@ -1804,7 +1820,7 @@
         <v>26.17308959555929</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2040</v>
       </c>
@@ -1818,10 +1834,10 @@
         <v>9</v>
       </c>
       <c r="E83">
-        <v>12.39348478178701</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>12.393484781787009</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2040</v>
       </c>
@@ -1838,7 +1854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2040</v>
       </c>
@@ -1855,7 +1871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2040</v>
       </c>
@@ -1872,7 +1888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2040</v>
       </c>
@@ -1886,10 +1902,10 @@
         <v>9</v>
       </c>
       <c r="E87">
-        <v>7.561070690885179</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>7.5610706908851792</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2040</v>
       </c>
@@ -1903,10 +1919,10 @@
         <v>9</v>
       </c>
       <c r="E88">
-        <v>90.52657241245544</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>90.526572412455437</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2040</v>
       </c>
@@ -1923,7 +1939,7 @@
         <v>4.166666666666667</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2040</v>
       </c>
@@ -1937,10 +1953,10 @@
         <v>9</v>
       </c>
       <c r="E90">
-        <v>259.1086646866131</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>259.10866468661311</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2040</v>
       </c>
@@ -1954,10 +1970,10 @@
         <v>9</v>
       </c>
       <c r="E91">
-        <v>13.68288565821299</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>13.682885658212991</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2045</v>
       </c>
@@ -1971,10 +1987,10 @@
         <v>9</v>
       </c>
       <c r="E92">
-        <v>8.500659755752796</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>8.5006597557527961</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2045</v>
       </c>
@@ -1991,7 +2007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2045</v>
       </c>
@@ -2008,7 +2024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2045</v>
       </c>
@@ -2025,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2045</v>
       </c>
@@ -2039,10 +2055,10 @@
         <v>9</v>
       </c>
       <c r="E96">
-        <v>5.63196167556061</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>5.6319616755606097</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2045</v>
       </c>
@@ -2056,10 +2072,10 @@
         <v>9</v>
       </c>
       <c r="E97">
-        <v>67.42989284062941</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>67.429892840629407</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2045</v>
       </c>
@@ -2076,7 +2092,7 @@
         <v>4.166666666666667</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2045</v>
       </c>
@@ -2090,10 +2106,10 @@
         <v>9</v>
       </c>
       <c r="E99">
-        <v>193.0004531077661</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <v>193.00045310776611</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2045</v>
       </c>
@@ -2107,10 +2123,10 @@
         <v>9</v>
       </c>
       <c r="E100">
-        <v>9.385056544247202</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>9.3850565442472025</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2050</v>
       </c>
@@ -2124,10 +2140,10 @@
         <v>9</v>
       </c>
       <c r="E101">
-        <v>5.294537267441871</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>5.2945372674418714</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2050</v>
       </c>
@@ -2144,7 +2160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2050</v>
       </c>
@@ -2161,7 +2177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2050</v>
       </c>
@@ -2178,7 +2194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2050</v>
       </c>
@@ -2192,10 +2208,10 @@
         <v>9</v>
       </c>
       <c r="E105">
-        <v>5.481037594191124</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+        <v>5.4810375941911236</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2050</v>
       </c>
@@ -2209,10 +2225,10 @@
         <v>9</v>
       </c>
       <c r="E106">
-        <v>65.6229212701416</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+        <v>65.622921270141603</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2050</v>
       </c>
@@ -2229,7 +2245,7 @@
         <v>4.166666666666667</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2050</v>
       </c>
@@ -2246,7 +2262,7 @@
         <v>187.8284690341556</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2050</v>
       </c>
@@ -2260,10 +2276,10 @@
         <v>9</v>
       </c>
       <c r="E109">
-        <v>5.845373542558128</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+        <v>5.8453735425581277</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2026</v>
       </c>
@@ -2277,10 +2293,10 @@
         <v>10</v>
       </c>
       <c r="E110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+        <v>1.004259139674806</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2026</v>
       </c>
@@ -2297,7 +2313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2026</v>
       </c>
@@ -2314,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2026</v>
       </c>
@@ -2331,7 +2347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2026</v>
       </c>
@@ -2345,10 +2361,10 @@
         <v>10</v>
       </c>
       <c r="E114">
-        <v>0.7863237762565295</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <v>0.78632377625652949</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2026</v>
       </c>
@@ -2362,10 +2378,10 @@
         <v>10</v>
       </c>
       <c r="E115">
-        <v>9.414433376047256</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <v>9.4144333760472563</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2026</v>
       </c>
@@ -2379,10 +2395,10 @@
         <v>10</v>
       </c>
       <c r="E116">
-        <v>1.111111111111111</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <v>1.1111111111111109</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2026</v>
       </c>
@@ -2396,10 +2412,10 @@
         <v>10</v>
       </c>
       <c r="E117">
-        <v>26.94635614540354</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
+        <v>26.946356145403541</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2026</v>
       </c>
@@ -2413,10 +2429,10 @@
         <v>10</v>
       </c>
       <c r="E118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
+        <v>1.108740860325194</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2030</v>
       </c>
@@ -2430,10 +2446,10 @@
         <v>10</v>
       </c>
       <c r="E119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
+        <v>0.60312581554535216</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2030</v>
       </c>
@@ -2450,7 +2466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2030</v>
       </c>
@@ -2467,7 +2483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2030</v>
       </c>
@@ -2484,7 +2500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2030</v>
       </c>
@@ -2498,10 +2514,10 @@
         <v>10</v>
       </c>
       <c r="E123">
-        <v>1.484470507347828</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
+        <v>1.4844705073478279</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2030</v>
       </c>
@@ -2515,10 +2531,10 @@
         <v>10</v>
       </c>
       <c r="E124">
-        <v>17.77314779500431</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
+        <v>17.773147795004309</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2030</v>
       </c>
@@ -2532,10 +2548,10 @@
         <v>10</v>
       </c>
       <c r="E125">
-        <v>2.222222222222222</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+        <v>2.2222222222222219</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2030</v>
       </c>
@@ -2549,10 +2565,10 @@
         <v>10</v>
       </c>
       <c r="E126">
-        <v>50.87099256845129</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+        <v>50.870992568451292</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2030</v>
       </c>
@@ -2566,10 +2582,10 @@
         <v>10</v>
       </c>
       <c r="E127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
+        <v>0.66587418445464774</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2035</v>
       </c>
@@ -2583,10 +2599,10 @@
         <v>10</v>
       </c>
       <c r="E128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
+        <v>0.93059128986430217</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2035</v>
       </c>
@@ -2603,7 +2619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2035</v>
       </c>
@@ -2620,7 +2636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2035</v>
       </c>
@@ -2637,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2035</v>
       </c>
@@ -2654,7 +2670,7 @@
         <v>1.470180788882288</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2035</v>
       </c>
@@ -2668,10 +2684,10 @@
         <v>10</v>
       </c>
       <c r="E133">
-        <v>17.60206101559042</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
+        <v>17.602061015590419</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2035</v>
       </c>
@@ -2688,7 +2704,7 @@
         <v>3.333333333333333</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2035</v>
       </c>
@@ -2702,10 +2718,10 @@
         <v>10</v>
       </c>
       <c r="E135">
-        <v>50.38130135648878</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+        <v>50.381301356488777</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2035</v>
       </c>
@@ -2719,10 +2735,10 @@
         <v>10</v>
       </c>
       <c r="E136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+        <v>1.0274087101356979</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2040</v>
       </c>
@@ -2736,10 +2752,10 @@
         <v>10</v>
       </c>
       <c r="E137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+        <v>1.0047235227889539</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2040</v>
       </c>
@@ -2756,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2040</v>
       </c>
@@ -2773,7 +2789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2040</v>
       </c>
@@ -2790,7 +2806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2040</v>
       </c>
@@ -2804,10 +2820,10 @@
         <v>10</v>
       </c>
       <c r="E141">
-        <v>0.8928594587863921</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+        <v>0.89285945878639206</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2040</v>
       </c>
@@ -2824,7 +2840,7 @@
         <v>10.68995513392159</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2040</v>
       </c>
@@ -2838,10 +2854,10 @@
         <v>10</v>
       </c>
       <c r="E143">
-        <v>3.888888888888889</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
+        <v>3.8888888888888888</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2040</v>
       </c>
@@ -2855,10 +2871,10 @@
         <v>10</v>
       </c>
       <c r="E144">
-        <v>30.5972039644917</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
+        <v>30.597203964491701</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2040</v>
       </c>
@@ -2872,10 +2888,10 @@
         <v>10</v>
       </c>
       <c r="E145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+        <v>1.109253557211046</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2045</v>
       </c>
@@ -2889,10 +2905,10 @@
         <v>10</v>
       </c>
       <c r="E146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+        <v>0.59763945233474225</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2045</v>
       </c>
@@ -2909,7 +2925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2045</v>
       </c>
@@ -2926,7 +2942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2045</v>
       </c>
@@ -2943,7 +2959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2045</v>
       </c>
@@ -2957,10 +2973,10 @@
         <v>10</v>
       </c>
       <c r="E150">
-        <v>0.4365368998486919</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
+        <v>0.43653689984869187</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2045</v>
       </c>
@@ -2974,10 +2990,10 @@
         <v>10</v>
       </c>
       <c r="E151">
-        <v>5.226533501730162</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
+        <v>5.2265335017301622</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2045</v>
       </c>
@@ -2991,10 +3007,10 @@
         <v>10</v>
       </c>
       <c r="E152">
-        <v>3.611111111111111</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
+        <v>3.6111111111111112</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2045</v>
       </c>
@@ -3011,7 +3027,7 @@
         <v>14.95958678743504</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2045</v>
       </c>
@@ -3025,10 +3041,10 @@
         <v>10</v>
       </c>
       <c r="E154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
+        <v>0.65981702766525785</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2050</v>
       </c>
@@ -3045,7 +3061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2050</v>
       </c>
@@ -3062,7 +3078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2050</v>
       </c>
@@ -3079,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2050</v>
       </c>
@@ -3096,7 +3112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2050</v>
       </c>
@@ -3110,10 +3126,10 @@
         <v>10</v>
       </c>
       <c r="E159">
-        <v>0.2686680781182683</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
+        <v>0.26866807811826832</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2050</v>
       </c>
@@ -3127,10 +3143,10 @@
         <v>10</v>
       </c>
       <c r="E160">
-        <v>3.216687321546693</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+        <v>3.2166873215466931</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2050</v>
       </c>
@@ -3147,7 +3163,7 @@
         <v>3.333333333333333</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2050</v>
       </c>
@@ -3161,10 +3177,10 @@
         <v>10</v>
       </c>
       <c r="E162">
-        <v>9.206927141821678</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
+        <v>9.2069271418216783</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2050</v>
       </c>
@@ -3181,7 +3197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2026</v>
       </c>
@@ -3195,10 +3211,10 @@
         <v>11</v>
       </c>
       <c r="E164">
-        <v>164.751729869112</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
+        <v>164.75172986911201</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2026</v>
       </c>
@@ -3215,7 +3231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2026</v>
       </c>
@@ -3232,7 +3248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2026</v>
       </c>
@@ -3249,7 +3265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2026</v>
       </c>
@@ -3263,10 +3279,10 @@
         <v>11</v>
       </c>
       <c r="E168">
-        <v>24.14108574697975</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
+        <v>24.141085746979751</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2026</v>
       </c>
@@ -3280,10 +3296,10 @@
         <v>11</v>
       </c>
       <c r="E169">
-        <v>289.0344286324099</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
+        <v>289.03442863240991</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2026</v>
       </c>
@@ -3297,10 +3313,10 @@
         <v>11</v>
       </c>
       <c r="E170">
-        <v>0.037</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2026</v>
       </c>
@@ -3314,10 +3330,10 @@
         <v>11</v>
       </c>
       <c r="E171">
-        <v>827.2855456206103</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
+        <v>827.28554562061026</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2026</v>
       </c>
@@ -3331,10 +3347,10 @@
         <v>11</v>
       </c>
       <c r="E172">
-        <v>181.8922701308881</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
+        <v>181.89227013088811</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2030</v>
       </c>
@@ -3348,10 +3364,10 @@
         <v>11</v>
       </c>
       <c r="E173">
-        <v>180.3828554154528</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
+        <v>180.38285541545281</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2030</v>
       </c>
@@ -3368,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2030</v>
       </c>
@@ -3385,7 +3401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2030</v>
       </c>
@@ -3402,7 +3418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2030</v>
       </c>
@@ -3419,7 +3435,7 @@
         <v>13.82385009432965</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2030</v>
       </c>
@@ -3436,7 +3452,7 @@
         <v>165.5090684566469</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2030</v>
       </c>
@@ -3453,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2030</v>
       </c>
@@ -3467,10 +3483,10 @@
         <v>11</v>
       </c>
       <c r="E180">
-        <v>473.7264714490234</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
+        <v>473.72647144902339</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2030</v>
       </c>
@@ -3484,10 +3500,10 @@
         <v>11</v>
       </c>
       <c r="E181">
-        <v>199.1496361845473</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
+        <v>199.14963618454729</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2035</v>
       </c>
@@ -3504,7 +3520,7 @@
         <v>140.6104754109173</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2035</v>
       </c>
@@ -3521,7 +3537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2035</v>
       </c>
@@ -3538,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2035</v>
       </c>
@@ -3555,7 +3571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2035</v>
       </c>
@@ -3569,10 +3585,10 @@
         <v>11</v>
       </c>
       <c r="E186">
-        <v>5.668829735225702</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
+        <v>5.6688297352257022</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2035</v>
       </c>
@@ -3586,10 +3602,10 @@
         <v>11</v>
       </c>
       <c r="E187">
-        <v>67.87130374781773</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
+        <v>67.871303747817734</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2035</v>
       </c>
@@ -3606,7 +3622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2035</v>
       </c>
@@ -3623,7 +3639,7 @@
         <v>194.2638765169566</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2035</v>
       </c>
@@ -3640,7 +3656,7 @@
         <v>155.2393932190827</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2040</v>
       </c>
@@ -3654,10 +3670,10 @@
         <v>11</v>
       </c>
       <c r="E191">
-        <v>77.98233130120468</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
+        <v>77.982331301204681</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2040</v>
       </c>
@@ -3674,7 +3690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2040</v>
       </c>
@@ -3691,7 +3707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2040</v>
       </c>
@@ -3708,7 +3724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2040</v>
       </c>
@@ -3722,10 +3738,10 @@
         <v>11</v>
       </c>
       <c r="E195">
-        <v>1.638094109445078</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5">
+        <v>1.6380941094450781</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2040</v>
       </c>
@@ -3739,10 +3755,10 @@
         <v>11</v>
       </c>
       <c r="E196">
-        <v>19.61243996777606</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5">
+        <v>19.612439967776059</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2040</v>
       </c>
@@ -3759,7 +3775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2040</v>
       </c>
@@ -3773,10 +3789,10 @@
         <v>11</v>
       </c>
       <c r="E198">
-        <v>56.13548592277887</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
+        <v>56.135485922778869</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2040</v>
       </c>
@@ -3790,10 +3806,10 @@
         <v>11</v>
       </c>
       <c r="E199">
-        <v>86.09550431879532</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
+        <v>86.095504318795321</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>2045</v>
       </c>
@@ -3810,7 +3826,7 @@
         <v>29.42410936394722</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>2045</v>
       </c>
@@ -3827,7 +3843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>2045</v>
       </c>
@@ -3844,7 +3860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>2045</v>
       </c>
@@ -3861,7 +3877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>2045</v>
       </c>
@@ -3875,10 +3891,10 @@
         <v>11</v>
       </c>
       <c r="E204">
-        <v>1.920218523244907</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5">
+        <v>1.9202185232449069</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>2045</v>
       </c>
@@ -3895,7 +3911,7 @@
         <v>22.99023621109907</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>2045</v>
       </c>
@@ -3912,7 +3928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2045</v>
       </c>
@@ -3926,10 +3942,10 @@
         <v>11</v>
       </c>
       <c r="E207">
-        <v>65.80354526565601</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5">
+        <v>65.803545265656012</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>2045</v>
       </c>
@@ -3943,10 +3959,10 @@
         <v>11</v>
       </c>
       <c r="E208">
-        <v>32.48535267605278</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5">
+        <v>32.485352676052777</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>2050</v>
       </c>
@@ -3963,7 +3979,7 @@
         <v>1.328835503507124</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>2050</v>
       </c>
@@ -3980,7 +3996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>2050</v>
       </c>
@@ -3997,7 +4013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>2050</v>
       </c>
@@ -4014,7 +4030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>2050</v>
       </c>
@@ -4031,7 +4047,7 @@
         <v>1.945821436888173</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>2050</v>
       </c>
@@ -4048,7 +4064,7 @@
         <v>23.29677269391372</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>2050</v>
       </c>
@@ -4065,7 +4081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>2050</v>
       </c>
@@ -4079,10 +4095,10 @@
         <v>11</v>
       </c>
       <c r="E216">
-        <v>66.68092586919809</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5">
+        <v>66.680925869198092</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>2050</v>
       </c>
@@ -4096,7 +4112,7 @@
         <v>11</v>
       </c>
       <c r="E217">
-        <v>1.467085696492877</v>
+        <v>1.4670856964928769</v>
       </c>
     </row>
   </sheetData>
